--- a/Solver/Min Solver.xlsx
+++ b/Solver/Min Solver.xlsx
@@ -8,13 +8,60 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Solver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE3D47C7-6525-4A41-945B-68DC3C8264BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A86B32-17E1-4B37-9127-776403CC2AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{2FFBAF1F-FB06-4C74-8F44-8244157ED8E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">Sheet1!$B$4:$E$6</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">Sheet1!$B$4:$E$4</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">Sheet1!$B$4:$E$6</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">Sheet1!$B$4:$E$6</definedName>
+    <definedName name="solver_lhs4" localSheetId="0" hidden="1">Sheet1!$B$5:$E$5</definedName>
+    <definedName name="solver_lhs5" localSheetId="0" hidden="1">Sheet1!$B$6:$E$6</definedName>
+    <definedName name="solver_lhs6" localSheetId="0" hidden="1">Sheet1!$B$7:$E$7</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">6</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">Sheet1!$H$7</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="0" hidden="1">4</definedName>
+    <definedName name="solver_rel3" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_rel4" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel5" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel6" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">92</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">"integer"</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">20</definedName>
+    <definedName name="solver_rhs4" localSheetId="0" hidden="1">45</definedName>
+    <definedName name="solver_rhs5" localSheetId="0" hidden="1">55</definedName>
+    <definedName name="solver_rhs6" localSheetId="0" hidden="1">Sheet1!$B$8:$E$8</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -530,82 +577,98 @@
         <v>6</v>
       </c>
       <c r="B4" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="C4" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="E4" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="G4" s="1">
         <v>1.25</v>
       </c>
-      <c r="H4" s="1"/>
+      <c r="H4" s="1">
+        <f>SUM(B4:E4)*G4</f>
+        <v>395</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1">
         <v>1.84</v>
       </c>
-      <c r="H5" s="1"/>
+      <c r="H5" s="1">
+        <f t="shared" ref="H5:H6" si="0">SUM(B5:E5)*G5</f>
+        <v>237.36</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="1">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="C6" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E6" s="1">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G6" s="1">
         <v>1.46</v>
       </c>
-      <c r="H6" s="1"/>
+      <c r="H6" s="1">
+        <f t="shared" si="0"/>
+        <v>270.09999999999997</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="1">
-        <v>0</v>
+        <f>SUM(B4:B6)</f>
+        <v>180</v>
       </c>
       <c r="C7" s="1">
-        <v>0</v>
+        <f t="shared" ref="C7:E7" si="1">SUM(C4:C6)</f>
+        <v>80</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>190</v>
       </c>
       <c r="E7" s="1">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
       <c r="G7" s="1"/>
-      <c r="H7" s="2"/>
+      <c r="H7" s="2">
+        <f>SUM(H4:H6)</f>
+        <v>902.46</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
